--- a/techniques_table.xlsx
+++ b/techniques_table.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4645,6 +4645,1702 @@
       </c>
       <c r="D142" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>T1007</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AN2076</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DET0933</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>System Service Enumeration</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>T1012</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AN2077</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>DET0934</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Registry Query for Sensitive Configurations</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>T1016</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AN2078</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DET0935</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>System Network Configuration Enumeration</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>T1018</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AN2079</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>DET0936</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Remote System Discovery via Native Tools</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>T1046</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AN2080</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>DET0937</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Local Network Service Port Discovery</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>T1049</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AN2081</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DET0938</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>SMB Share and Session Discovery</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>T1069</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AN2082</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>DET0939</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Local and Domain Group Discovery</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>T1082</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AN2083</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>DET0940</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>System and Hardware Information Enumeration</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>T1083</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AN2084</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>DET0941</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Recursive Directory Enumeration</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>T1087</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AN2085</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>DET0942</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Local and Domain Account Enumeration</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>T1120</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AN2086</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>DET0943</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Peripheral Device Discovery via PowerShell or WMI</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>T1135</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AN2087</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DET0944</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Network Share Enumeration via Native Tools</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>T1614</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AN2088</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>DET0945</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>System Locale and Keyboard Layout Discovery</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>T1124</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AN2089</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>DET0946</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>System Time and Timezone Discovery</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>T1615</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AN2090</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DET0947</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Group Policy Enumeration</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>T1654</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AN2091</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>DET0948</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Windows Event Log Enumeration</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>T1652</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AN2092</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>DET0949</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Device Driver Enumeration</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>T1040</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AN2093</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DET0950</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Network Packet Capture Tool Execution</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>T1497</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AN2094</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DET0951</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>VM and Sandbox Detection Artifact Queries</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>T1673</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AN2095</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>DET0952</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Virtual Machine Infrastructure Enumeration</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>T1680</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AN2096</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DET0953</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Local Storage Device Enumeration</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>T1622</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Discovery</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AN2097</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DET0954</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Debugger Presence Check via Registry or Process Query</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>T1197</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AN2098</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DET0955</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>BITS Job Transfer or Notification Command Abuse</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>T1140</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AN2099</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DET0956</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>File Decode or Deobfuscation via LOLBins</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>T1202</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AN2100</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>DET0957</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Indirect Command Execution via Trusted Windows Utilities</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>T1216</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AN2101</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DET0958</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Microsoft-Signed Script Proxy Execution</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>T1220</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AN2102</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>DET0959</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>XSL Script Execution via WMIC or MSXSL</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>T1552</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AN2103</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DET0960</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Credential String Search in Files and Registry</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>T1187</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AN2104</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>DET0961</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Forced Authentication via UNC Path or SCF File Creation</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>T1036</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AN2105</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>DET0962</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>System Binary Name Used from Non-Standard Path</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>T1027</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AN2106</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DET0963</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PowerShell Encoded Command or Heavy Obfuscation Execution</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>T1539</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AN2107</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DET0964</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Browser Cookie Database Access by Non-Browser Process</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>T1001</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AN2108</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DET0965</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Steganography or Data Obfuscation Utility Execution</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>T1006</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AN2109</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DET0966</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Direct Volume Access Command Line Detection</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>T1008</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Command and Control</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AN2110</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DET0967</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Redundant Fallback Channel Proxy Execution</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>T1014</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AN2111</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DET0968</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Rootkit Installation or Kernel Driver Bypass Tool Execution</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>T1037</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AN2112</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DET0969</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>User Logon Initialization Script Registry Modification</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>T1092</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Command and Control</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AN2113</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DET0970</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Script or Binary Execution from Removable Media Path</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>T1098</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AN2114</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>DET0971</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Privileged Account or Group Membership Manipulation</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>T1111</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AN2115</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>DET0972</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Custom Security Support Provider or LSA Package Registration</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>T1132</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Command and Control</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AN2116</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>DET0973</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Process Command Line Data Encoding or Decoding Activity</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>T1211</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AN2117</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>DET0974</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Anomalous Handle Access to System Process for Exploitation or Stealth</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>T1212</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AN2118</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DET0975</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Print Spooler Service Spawning Suspicious Child Process</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>T1221</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AN2119</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DET0976</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Microsoft Office Application Spawning Script Interpreter</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>T1480</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AN2120</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>DET0977</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Execution Guardrails Target Discovery Query</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>T1542</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Persistence</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AN2121</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>DET0978</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>System Firmware or BIOS Flash Utility Execution</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>T1620</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AN2122</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DET0979</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>PowerShell Reflective Code Loading API Call</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>T1649</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AN2123</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>DET0980</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Authentication Certificate or Private Key Export Tool Execution</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>T1665</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AN2124</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>DET0981</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Network DNS Resolver or Interface Routing Hijack</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>T1674</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AN2125</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>DET0982</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Input Keystroke Automation or Injection Tool Execution</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>T1678</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AN2126</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>DET0983</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Artificial Execution Delay or Anti-Sandbox Sleep</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>T1679</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Stealth</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AN2127</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>DET0984</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Windows Defender Selective Exclusion Configuration</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>T1684</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Credential Access</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AN2128</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DET0985</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Social Engineering Script-Based Credential Dialog Prompt</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4661,7 +6357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4692,1172 +6388,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>T1001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Data Obfuscation</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Command and Control</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>T1006</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Direct Volume Access</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>T1007</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>System Service Discovery</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>T1008</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fallback Channels</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Command and Control</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>T1012</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Query Registry</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>T1014</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rootkit</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>T1016</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>System Network Configuration Discovery</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T1018</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Remote System Discovery</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>T1027</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Obfuscated Files or Information</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T1036</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Masquerading</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T1037</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Boot or Logon Initialization Scripts</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Persistence, Privilege Escalation</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T1040</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Network Sniffing</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Credential Access, Discovery</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T1046</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Network Service Discovery</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T1049</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>System Network Connections Discovery</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T1069</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Permission Groups Discovery</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T1082</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>System Information Discovery</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>T1083</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>File and Directory Discovery</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>T1087</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Account Discovery</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>T1092</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Communication Through Removable Media</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Command and Control</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>T1098</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Account Manipulation</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Persistence, Privilege Escalation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>T1111</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Multi-Factor Authentication Interception</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>T1120</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Peripheral Device Discovery</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>T1124</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>System Time Discovery</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>T1132</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Data Encoding</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Command and Control</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>T1135</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Network Share Discovery</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>T1140</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Deobfuscate/Decode Files or Information</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>T1187</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Forced Authentication</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>T1197</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>BITS Jobs</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Execution, Persistence, Stealth</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>T1202</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Indirect Command Execution</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>T1211</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Exploitation for Stealth</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>T1212</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Exploitation for Credential Access</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>T1216</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>System Script Proxy Execution</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>T1220</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>XSL Script Processing</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>T1221</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Template Injection</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>T1480</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Execution Guardrails</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>T1497</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Virtualization/Sandbox Evasion</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Discovery, Stealth</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>T1539</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Steal Web Session Cookie</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>T1542</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Pre-OS Boot</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Persistence, Stealth</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>T1552</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Unsecured Credentials</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>T1614</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>System Location Discovery</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>T1615</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Group Policy Discovery</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>T1620</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Reflective Code Loading</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>T1622</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Debugger Evasion</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Discovery, Stealth</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>T1649</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Steal or Forge Authentication Certificates</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Credential Access</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>T1652</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Device Driver Discovery</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>T1654</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Log Enumeration</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>T1665</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Hide Infrastructure</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Command and Control</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>T1673</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Virtual Machine Discovery</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>T1674</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Input Injection</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>T1678</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Delay Execution</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>T1679</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Selective Exclusion</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>T1680</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Local Storage Discovery</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Discovery</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>T1684</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Social Engineering</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Stealth</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Windows</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/techniques_table.xlsx
+++ b/techniques_table.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Covered Techniques" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Uncovered Techniques" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -123,34 +134,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CoveredTechniquesTable" displayName="CoveredTechniquesTable" ref="A1:F128" headerRowCount="1">
-  <autoFilter ref="A1:F128"/>
-  <tableColumns count="6">
-    <tableColumn id="1" name="Parent ID"/>
-    <tableColumn id="2" name="Technique Name"/>
-    <tableColumn id="3" name="Tactics"/>
-    <tableColumn id="4" name="Subtechniques Covered"/>
-    <tableColumn id="5" name="Rules Count"/>
-    <tableColumn id="6" name="Rule Sources"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="UncoveredTechniquesTable" displayName="UncoveredTechniquesTable" ref="A1:D63" headerRowCount="1">
-  <autoFilter ref="A1:D63"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="Parent ID"/>
-    <tableColumn id="2" name="Technique Name"/>
-    <tableColumn id="3" name="Tactics"/>
-    <tableColumn id="4" name="Platform"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,42 +427,34 @@
   </sheetPr>
   <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="61" customWidth="1" min="3" max="3"/>
-    <col width="63" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parent ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Technique Name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Tactics</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Subtechniques Covered</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Rules Count</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rule Sources</t>
         </is>
@@ -3709,7 +3684,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3739,7 +3714,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4546,6 +4521,8 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4566,6 +4543,8 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4586,6 +4565,8 @@
       <c r="D139" t="n">
         <v>1</v>
       </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4606,6 +4587,8 @@
       <c r="D140" t="n">
         <v>1</v>
       </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4626,6 +4609,8 @@
       <c r="D141" t="n">
         <v>1</v>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4646,6 +4631,8 @@
       <c r="D142" t="n">
         <v>1</v>
       </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6345,53 +6332,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Parent ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Technique Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Tactics</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Platform</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>